--- a/xls/square_12_tri3_17.xlsx
+++ b/xls/square_12_tri3_17.xlsx
@@ -482,13 +482,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-1.527122182604552</v>
+        <v>-1.527122364613141</v>
       </c>
       <c r="J17">
-        <v>-1.6393942260721304</v>
+        <v>-1.6393942775106876</v>
       </c>
       <c r="K17">
-        <v>2.502842170839991</v>
+        <v>2.502842167386268</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-1.3699062721543782</v>
+        <v>-1.3699060526497207</v>
       </c>
       <c r="J18">
-        <v>-1.0795732510533749</v>
+        <v>-1.0795731341751411</v>
       </c>
       <c r="K18">
-        <v>3.4185667730697507</v>
+        <v>3.4185667321935744</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.3101824974345483</v>
+        <v>-0.31018249913162366</v>
       </c>
       <c r="J19">
-        <v>-0.24199244354849792</v>
+        <v>-0.24199244462809238</v>
       </c>
       <c r="K19">
-        <v>3.8814397255902144</v>
+        <v>3.8814397267527267</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>0.000497019154179596</v>
+        <v>0.0004970191508447201</v>
       </c>
       <c r="J20">
-        <v>8.545776425410807e-5</v>
+        <v>8.545776243632278e-5</v>
       </c>
       <c r="K20">
-        <v>2.7336087111511667</v>
+        <v>2.733608711127936</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.00040136887195201416</v>
+        <v>-0.00040136887177948127</v>
       </c>
       <c r="J21">
-        <v>-0.0003193321887868788</v>
+        <v>-0.0003193321886926912</v>
       </c>
       <c r="K21">
-        <v>2.6224290422393506</v>
+        <v>2.6224290422883123</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.00025904473816191126</v>
+        <v>-0.00025904473791836974</v>
       </c>
       <c r="J22">
-        <v>-0.0001825937969873603</v>
+        <v>-0.0001825937968512847</v>
       </c>
       <c r="K22">
-        <v>2.4391279012838307</v>
+        <v>2.4391279014578937</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.0005507799566506506</v>
+        <v>-0.000550779956636119</v>
       </c>
       <c r="J23">
-        <v>-0.0004212242982576822</v>
+        <v>-0.0004212242982520354</v>
       </c>
       <c r="K23">
-        <v>2.6547146763901037</v>
+        <v>2.6547146766491996</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.00010886204641657993</v>
+        <v>-0.00010886204642665968</v>
       </c>
       <c r="J24">
-        <v>-8.609306118882909e-5</v>
+        <v>-8.609306119601474e-5</v>
       </c>
       <c r="K24">
-        <v>2.3315924370957357</v>
+        <v>2.3315924369102117</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -762,13 +762,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>3.025396970696581e-6</v>
+        <v>3.0253969641392e-6</v>
       </c>
       <c r="J25">
-        <v>-5.3968063320495136e-6</v>
+        <v>-5.396806335424702e-6</v>
       </c>
       <c r="K25">
-        <v>2.044168123956738</v>
+        <v>2.0441681238429386</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.0001131613261259088</v>
+        <v>-0.00011316132613145512</v>
       </c>
       <c r="J26">
-        <v>-7.941683724520681e-5</v>
+        <v>-7.941683724916128e-5</v>
       </c>
       <c r="K26">
-        <v>2.2574259541773816</v>
+        <v>2.2574259542226804</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -832,13 +832,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-5.997942476133482e-6</v>
+        <v>-5.997942476374567e-6</v>
       </c>
       <c r="J27">
-        <v>-5.0520172796527335e-6</v>
+        <v>-5.052017279604516e-6</v>
       </c>
       <c r="K27">
-        <v>1.7530938377496552</v>
+        <v>1.7530938379385574</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -867,13 +867,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-1.9621093653608058e-6</v>
+        <v>-1.962109365457239e-6</v>
       </c>
       <c r="J28">
-        <v>-1.8250577919298438e-6</v>
+        <v>-1.825057791785194e-6</v>
       </c>
       <c r="K28">
-        <v>1.5804314405301723</v>
+        <v>1.5804314405821702</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-5.337416520236689e-6</v>
+        <v>-5.337416520284905e-6</v>
       </c>
       <c r="J29">
-        <v>-4.386541599196561e-6</v>
+        <v>-4.3865415990519105e-6</v>
       </c>
       <c r="K29">
-        <v>1.7249526443657346</v>
+        <v>1.7249526444060064</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -937,13 +937,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-1.759009601501231e-6</v>
+        <v>-1.7590096013083645e-6</v>
       </c>
       <c r="J30">
-        <v>-2.303205490240935e-6</v>
+        <v>-2.3032054900962852e-6</v>
       </c>
       <c r="K30">
-        <v>1.7048539010270845</v>
+        <v>1.7048539010986041</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -972,13 +972,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-3.0072224940788366e-6</v>
+        <v>-3.0072224939341867e-6</v>
       </c>
       <c r="J31">
-        <v>-2.7815080411517907e-6</v>
+        <v>-2.781508041296441e-6</v>
       </c>
       <c r="K31">
-        <v>1.6825650188458425</v>
+        <v>1.682565019006375</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-1.3322024909911724e-5</v>
+        <v>-1.3322024910104595e-5</v>
       </c>
       <c r="J32">
-        <v>-1.0748572972581437e-5</v>
+        <v>-1.074857297291896e-5</v>
       </c>
       <c r="K32">
-        <v>1.8934903285362124</v>
+        <v>1.8934903283341993</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_17.xlsx
+++ b/xls/square_12_tri3_17.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>324</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>169</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>1350</v>
+      </c>
+      <c r="I15">
+        <v>2.590212841017628</v>
+      </c>
+      <c r="J15">
+        <v>-0.6068167248495597</v>
+      </c>
+      <c r="K15">
+        <v>3.4042605607680465</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>324</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>169</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>1536</v>
+      </c>
+      <c r="I16">
+        <v>1.165280509248601</v>
+      </c>
+      <c r="J16">
+        <v>-1.4247839519162866</v>
+      </c>
+      <c r="K16">
+        <v>2.5137418494348527</v>
+      </c>
+    </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>11</v>
